--- a/AtchisonRegime/Outputs/UK/MSCI_UK 100/df_regEquityReturns_MSCI_UK 100.xlsx
+++ b/AtchisonRegime/Outputs/UK/MSCI_UK 100/df_regEquityReturns_MSCI_UK 100.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q341"/>
+  <dimension ref="A1:Q342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19282,7 +19282,7 @@
         <v>-1.19358360560507</v>
       </c>
       <c r="C331" t="n">
-        <v>0.09340882308341358</v>
+        <v>0.07964939555553918</v>
       </c>
       <c r="D331" t="b">
         <v>0</v>
@@ -19339,7 +19339,7 @@
         <v>-1.346897329223275</v>
       </c>
       <c r="C332" t="n">
-        <v>0.0900835623051776</v>
+        <v>0.09572965693366631</v>
       </c>
       <c r="D332" t="b">
         <v>0</v>
@@ -19396,7 +19396,7 @@
         <v>-1.368891981285238</v>
       </c>
       <c r="C333" t="n">
-        <v>0.06848008446736131</v>
+        <v>0.07146216020915283</v>
       </c>
       <c r="D333" t="b">
         <v>0</v>
@@ -19453,7 +19453,7 @@
         <v>-1.329356106593292</v>
       </c>
       <c r="C334" t="n">
-        <v>0.01849161531362393</v>
+        <v>0.02267314646484296</v>
       </c>
       <c r="D334" t="b">
         <v>0</v>
@@ -19510,7 +19510,7 @@
         <v>-1.347299861214833</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.02802955874058935</v>
+        <v>-0.02431350306585164</v>
       </c>
       <c r="D335" t="b">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>-1.315386399498972</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.04706984423541187</v>
+        <v>-0.04243801116167915</v>
       </c>
       <c r="D336" t="b">
         <v>0</v>
@@ -19624,7 +19624,7 @@
         <v>-1.232105420566099</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.04248868081484558</v>
+        <v>-0.03692774043661936</v>
       </c>
       <c r="D337" t="b">
         <v>0</v>
@@ -19681,7 +19681,7 @@
         <v>-1.078242244087746</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.02351694915932823</v>
+        <v>-0.02134923865410661</v>
       </c>
       <c r="D338" t="b">
         <v>0</v>
@@ -19738,7 +19738,7 @@
         <v>-0.9627195965964149</v>
       </c>
       <c r="C339" t="n">
-        <v>0.009301455898754887</v>
+        <v>0.0003254350348723328</v>
       </c>
       <c r="D339" t="b">
         <v>0</v>
@@ -19795,7 +19795,7 @@
         <v>-0.9042649416713244</v>
       </c>
       <c r="C340" t="n">
-        <v>0.03660336726301534</v>
+        <v>0.01834838496226009</v>
       </c>
       <c r="D340" t="b">
         <v>0</v>
@@ -19849,10 +19849,10 @@
         <v>45747</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.8397481983321728</v>
+        <v>-0.8737728267695283</v>
       </c>
       <c r="C341" t="n">
-        <v>0.04503902734193773</v>
+        <v>0.0005865205272010107</v>
       </c>
       <c r="D341" t="b">
         <v>0</v>
@@ -19898,6 +19898,63 @@
         <v>138.8398908696637</v>
       </c>
       <c r="Q341" t="n">
+        <v>78.13608554835069</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.8881880024222687</v>
+      </c>
+      <c r="C342" t="n">
+        <v>-0.02246363804680394</v>
+      </c>
+      <c r="D342" t="b">
+        <v>0</v>
+      </c>
+      <c r="E342" t="b">
+        <v>1</v>
+      </c>
+      <c r="F342" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="G342" t="n">
+        <v>244728.5126787703</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K342" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="L342" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" t="n">
+        <v>0</v>
+      </c>
+      <c r="N342" t="n">
+        <v>134.2397356408041</v>
+      </c>
+      <c r="O342" t="n">
+        <v>165.5810152529656</v>
+      </c>
+      <c r="P342" t="n">
+        <v>138.8398908696637</v>
+      </c>
+      <c r="Q342" t="n">
         <v>78.13608554835069</v>
       </c>
     </row>
